--- a/docs/d/218/inyear.xlsx
+++ b/docs/d/218/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 88 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 85 clubs short</t>
         </is>
       </c>
     </row>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3525,8 +3525,8 @@
       <c r="Y29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z29" s="9" t="n">
-        <v>0</v>
+      <c r="Z29" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA29" s="10" t="n">
         <v>1</v>
@@ -5354,7 +5354,7 @@
         <v>1</v>
       </c>
       <c r="U48" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V48" s="9" t="n">
         <v>3</v>
@@ -5506,13 +5506,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>0</v>
       </c>
       <c r="V50" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W50" s="9" t="n">
         <v>0</v>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -6899,8 +6899,8 @@
       <c r="R64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S64" s="9" t="n">
-        <v>1</v>
+      <c r="S64" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T64" s="9" t="n">
         <v>0</v>
@@ -10189,7 +10189,7 @@
         </is>
       </c>
       <c r="P98" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q98" s="9" t="n">
         <v>1</v>
@@ -11991,7 +11991,7 @@
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12061,8 +12061,8 @@
       <c r="Y117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z117" s="9" t="n">
-        <v>0</v>
+      <c r="Z117" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA117" s="10" t="n">
         <v>1</v>
@@ -13640,7 +13640,7 @@
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>10</v>
@@ -13710,8 +13710,8 @@
       <c r="Y134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z134" s="9" t="n">
-        <v>0</v>
+      <c r="Z134" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA134" s="10" t="n">
         <v>1</v>
@@ -14430,13 +14430,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L142" s="7" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>0</v>
       </c>
       <c r="V142" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W142" s="9" t="n">
         <v>0</v>
@@ -18368,7 +18368,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -18599,7 +18599,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -18995,7 +18995,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -19127,7 +19127,7 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>

--- a/docs/d/218/inyear.xlsx
+++ b/docs/d/218/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/218/inyear.xlsx
+++ b/docs/d/218/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 9 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 9 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 85 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 74 clubs short</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2555,8 +2555,8 @@
       <c r="Y19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z19" s="9" t="n">
-        <v>0</v>
+      <c r="Z19" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA19" s="10" t="n">
         <v>1</v>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>3</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
@@ -2932,13 +2932,13 @@
         <v>0</v>
       </c>
       <c r="V23" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W23" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X23" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y23" s="9" t="n">
         <v>0</v>
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40" s="6" t="n">
         <v>10</v>
@@ -4592,8 +4592,8 @@
       <c r="Y40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z40" s="9" t="n">
-        <v>0</v>
+      <c r="Z40" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA40" s="10" t="n">
         <v>1</v>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="P41" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q41" s="9" t="n">
         <v>0</v>
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>10</v>
@@ -4980,8 +4980,8 @@
       <c r="Y44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z44" s="9" t="n">
-        <v>0</v>
+      <c r="Z44" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA44" s="10" t="n">
         <v>1</v>
@@ -6074,7 +6074,7 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6144,8 +6144,8 @@
       <c r="Y56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z56" s="9" t="n">
-        <v>0</v>
+      <c r="Z56" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA56" s="10" t="n">
         <v>1</v>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -7017,8 +7017,8 @@
       <c r="Y65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z65" s="9" t="n">
-        <v>0</v>
+      <c r="Z65" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA65" s="10" t="n">
         <v>1</v>
@@ -7206,7 +7206,7 @@
         <v>0</v>
       </c>
       <c r="X67" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y67" s="9" t="n">
         <v>0</v>
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9248,8 +9248,8 @@
       <c r="Y88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z88" s="9" t="n">
-        <v>0</v>
+      <c r="Z88" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA88" s="10" t="n">
         <v>1</v>
@@ -10827,7 +10827,7 @@
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -10897,8 +10897,8 @@
       <c r="Y105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z105" s="9" t="n">
-        <v>0</v>
+      <c r="Z105" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA105" s="10" t="n">
         <v>1</v>
@@ -11259,7 +11259,7 @@
         <v>0</v>
       </c>
       <c r="Q109" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R109" s="9" t="n">
         <v>0</v>
@@ -12088,7 +12088,7 @@
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12158,8 +12158,8 @@
       <c r="Y118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z118" s="9" t="n">
-        <v>0</v>
+      <c r="Z118" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA118" s="10" t="n">
         <v>1</v>
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F142" s="6" t="n">
         <v>10</v>
@@ -14430,13 +14430,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L142" s="7" t="inlineStr">
         <is>
@@ -14474,8 +14474,8 @@
       <c r="U142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V142" s="9" t="n">
-        <v>3</v>
+      <c r="V142" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W142" s="9" t="n">
         <v>0</v>
@@ -14804,7 +14804,7 @@
         </is>
       </c>
       <c r="E146" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F146" s="6" t="n">
         <v>10</v>
@@ -14874,8 +14874,8 @@
       <c r="Y146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z146" s="9" t="n">
-        <v>0</v>
+      <c r="Z146" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA146" s="10" t="n">
         <v>1</v>
@@ -15257,7 +15257,7 @@
         <v>0</v>
       </c>
       <c r="X150" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y150" s="9" t="n">
         <v>0</v>
@@ -16065,7 +16065,7 @@
         </is>
       </c>
       <c r="E159" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F159" s="6" t="n">
         <v>10</v>
@@ -16135,8 +16135,8 @@
       <c r="Y159" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z159" s="9" t="n">
-        <v>0</v>
+      <c r="Z159" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA159" s="10" t="n">
         <v>1</v>
@@ -16162,7 +16162,7 @@
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F160" s="6" t="n">
         <v>10</v>
@@ -16232,8 +16232,8 @@
       <c r="Y160" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z160" s="9" t="n">
-        <v>0</v>
+      <c r="Z160" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA160" s="10" t="n">
         <v>1</v>
@@ -18302,7 +18302,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -18467,7 +18467,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5</v>
+        <v>0.83</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -18566,7 +18566,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -18632,7 +18632,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -18797,7 +18797,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -18896,7 +18896,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -18995,7 +18995,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -19160,7 +19160,7 @@
         <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -19193,7 +19193,7 @@
         <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -19292,7 +19292,7 @@
         <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>

--- a/docs/d/218/inyear.xlsx
+++ b/docs/d/218/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 9 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 9 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 74 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 33 clubs short</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -906,8 +906,8 @@
       <c r="Y2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" s="9" t="n">
-        <v>0</v>
+      <c r="Z2" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA2" s="10" t="n">
         <v>1</v>
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1294,8 +1294,8 @@
       <c r="Y6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z6" s="9" t="n">
-        <v>0</v>
+      <c r="Z6" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA6" s="10" t="n">
         <v>1</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1488,8 +1488,8 @@
       <c r="Y8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z8" s="9" t="n">
-        <v>0</v>
+      <c r="Z8" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA8" s="10" t="n">
         <v>1</v>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1585,8 +1585,8 @@
       <c r="Y9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z9" s="9" t="n">
-        <v>0</v>
+      <c r="Z9" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA9" s="10" t="n">
         <v>1</v>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>10</v>
@@ -2264,8 +2264,8 @@
       <c r="Y16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z16" s="9" t="n">
-        <v>0</v>
+      <c r="Z16" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA16" s="10" t="n">
         <v>1</v>
@@ -2550,7 +2550,7 @@
         <v>0</v>
       </c>
       <c r="X19" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y19" s="9" t="n">
         <v>0</v>
@@ -2679,7 +2679,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2749,8 +2749,8 @@
       <c r="Y21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z21" s="9" t="n">
-        <v>0</v>
+      <c r="Z21" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA21" s="10" t="n">
         <v>1</v>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3132,13 +3132,13 @@
         <v>0</v>
       </c>
       <c r="X25" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z25" s="9" t="n">
-        <v>0</v>
+      <c r="Z25" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA25" s="10" t="n">
         <v>1</v>
@@ -3884,7 +3884,7 @@
         </is>
       </c>
       <c r="P33" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q33" s="9" t="n">
         <v>1</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4107,8 +4107,8 @@
       <c r="Y35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z35" s="9" t="n">
-        <v>0</v>
+      <c r="Z35" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA35" s="10" t="n">
         <v>1</v>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="P37" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q37" s="9" t="n">
         <v>0</v>
@@ -4425,7 +4425,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4439,13 +4439,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>0</v>
       </c>
       <c r="V39" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W39" s="9" t="n">
         <v>0</v>
@@ -4495,8 +4495,8 @@
       <c r="Y39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z39" s="9" t="n">
-        <v>0</v>
+      <c r="Z39" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA39" s="10" t="n">
         <v>1</v>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5174,8 +5174,8 @@
       <c r="Y46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z46" s="9" t="n">
-        <v>0</v>
+      <c r="Z46" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA46" s="10" t="n">
         <v>1</v>
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>10</v>
@@ -5562,8 +5562,8 @@
       <c r="Y50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z50" s="9" t="n">
-        <v>0</v>
+      <c r="Z50" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA50" s="10" t="n">
         <v>1</v>
@@ -5783,7 +5783,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -5853,8 +5853,8 @@
       <c r="Y53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z53" s="9" t="n">
-        <v>0</v>
+      <c r="Z53" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA53" s="10" t="n">
         <v>1</v>
@@ -6241,8 +6241,8 @@
       <c r="Y57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z57" s="9" t="n">
-        <v>0</v>
+      <c r="Z57" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA57" s="9" t="n">
         <v>0</v>
@@ -6365,7 +6365,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6435,8 +6435,8 @@
       <c r="Y59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z59" s="9" t="n">
-        <v>0</v>
+      <c r="Z59" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA59" s="10" t="n">
         <v>1</v>
@@ -6462,7 +6462,7 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6532,8 +6532,8 @@
       <c r="Y60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z60" s="9" t="n">
-        <v>0</v>
+      <c r="Z60" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA60" s="10" t="n">
         <v>1</v>
@@ -6706,7 +6706,7 @@
         <v>0</v>
       </c>
       <c r="S62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T62" s="9" t="n">
         <v>0</v>
@@ -7044,7 +7044,7 @@
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7114,8 +7114,8 @@
       <c r="Y66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z66" s="9" t="n">
-        <v>0</v>
+      <c r="Z66" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA66" s="10" t="n">
         <v>1</v>
@@ -7432,7 +7432,7 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7502,8 +7502,8 @@
       <c r="Y70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z70" s="9" t="n">
-        <v>0</v>
+      <c r="Z70" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA70" s="10" t="n">
         <v>1</v>
@@ -8014,7 +8014,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8084,8 +8084,8 @@
       <c r="Y76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z76" s="9" t="n">
-        <v>0</v>
+      <c r="Z76" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA76" s="10" t="n">
         <v>1</v>
@@ -8176,7 +8176,7 @@
         <v>0</v>
       </c>
       <c r="X77" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y77" s="9" t="n">
         <v>0</v>
@@ -8208,7 +8208,7 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8278,8 +8278,8 @@
       <c r="Y78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z78" s="9" t="n">
-        <v>0</v>
+      <c r="Z78" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA78" s="10" t="n">
         <v>1</v>
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8346,7 +8346,7 @@
         </is>
       </c>
       <c r="P79" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q79" s="9" t="n">
         <v>0</v>
@@ -8375,8 +8375,8 @@
       <c r="Y79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z79" s="9" t="n">
-        <v>0</v>
+      <c r="Z79" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA79" s="10" t="n">
         <v>1</v>
@@ -9275,7 +9275,7 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9345,8 +9345,8 @@
       <c r="Y89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z89" s="9" t="n">
-        <v>0</v>
+      <c r="Z89" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA89" s="10" t="n">
         <v>1</v>
@@ -9469,7 +9469,7 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -9539,8 +9539,8 @@
       <c r="Y91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z91" s="9" t="n">
-        <v>0</v>
+      <c r="Z91" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA91" s="10" t="n">
         <v>1</v>
@@ -9954,7 +9954,7 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -10024,8 +10024,8 @@
       <c r="Y96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z96" s="9" t="n">
-        <v>0</v>
+      <c r="Z96" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA96" s="10" t="n">
         <v>1</v>
@@ -10245,7 +10245,7 @@
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10310,13 +10310,13 @@
         <v>0</v>
       </c>
       <c r="X99" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z99" s="9" t="n">
-        <v>0</v>
+      <c r="Z99" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA99" s="10" t="n">
         <v>1</v>
@@ -10439,7 +10439,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -10509,8 +10509,8 @@
       <c r="Y101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z101" s="9" t="n">
-        <v>0</v>
+      <c r="Z101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA101" s="10" t="n">
         <v>1</v>
@@ -10730,7 +10730,7 @@
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -10771,7 +10771,7 @@
         </is>
       </c>
       <c r="P104" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q104" s="9" t="n">
         <v>0</v>
@@ -10785,8 +10785,8 @@
       <c r="T104" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U104" s="9" t="n">
-        <v>0</v>
+      <c r="U104" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V104" s="9" t="n">
         <v>0</v>
@@ -10924,7 +10924,7 @@
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -10967,8 +10967,8 @@
       <c r="P106" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q106" s="9" t="n">
-        <v>1</v>
+      <c r="Q106" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R106" s="9" t="n">
         <v>0</v>
@@ -11215,7 +11215,7 @@
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11285,8 +11285,8 @@
       <c r="Y109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z109" s="9" t="n">
-        <v>0</v>
+      <c r="Z109" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA109" s="10" t="n">
         <v>1</v>
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -11576,8 +11576,8 @@
       <c r="Y112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z112" s="9" t="n">
-        <v>0</v>
+      <c r="Z112" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA112" s="10" t="n">
         <v>1</v>
@@ -12379,7 +12379,7 @@
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -12449,8 +12449,8 @@
       <c r="Y121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z121" s="9" t="n">
-        <v>0</v>
+      <c r="Z121" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA121" s="10" t="n">
         <v>1</v>
@@ -12476,7 +12476,7 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -12546,8 +12546,8 @@
       <c r="Y122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z122" s="9" t="n">
-        <v>0</v>
+      <c r="Z122" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA122" s="10" t="n">
         <v>1</v>
@@ -13058,7 +13058,7 @@
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13128,8 +13128,8 @@
       <c r="Y128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z128" s="9" t="n">
-        <v>0</v>
+      <c r="Z128" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA128" s="10" t="n">
         <v>1</v>
@@ -13587,7 +13587,7 @@
         <v>1</v>
       </c>
       <c r="Q133" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R133" s="9" t="n">
         <v>0</v>
@@ -13834,7 +13834,7 @@
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -13886,8 +13886,8 @@
       <c r="S136" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T136" s="9" t="n">
-        <v>0</v>
+      <c r="T136" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U136" s="9" t="n">
         <v>0</v>
@@ -14028,7 +14028,7 @@
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14098,8 +14098,8 @@
       <c r="Y138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z138" s="9" t="n">
-        <v>0</v>
+      <c r="Z138" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA138" s="10" t="n">
         <v>1</v>
@@ -14222,7 +14222,7 @@
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F140" s="6" t="n">
         <v>10</v>
@@ -14292,8 +14292,8 @@
       <c r="Y140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z140" s="9" t="n">
-        <v>0</v>
+      <c r="Z140" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA140" s="10" t="n">
         <v>1</v>
@@ -14430,17 +14430,17 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L142" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L142" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M142" s="8" t="n">
@@ -14478,7 +14478,7 @@
         <v>4</v>
       </c>
       <c r="W142" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X142" s="10" t="n">
         <v>7</v>
@@ -14845,7 +14845,7 @@
         </is>
       </c>
       <c r="P146" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q146" s="9" t="n">
         <v>0</v>
@@ -15095,7 +15095,7 @@
         </is>
       </c>
       <c r="E149" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F149" s="6" t="n">
         <v>10</v>
@@ -15160,13 +15160,13 @@
         <v>0</v>
       </c>
       <c r="X149" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y149" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z149" s="9" t="n">
-        <v>0</v>
+      <c r="Z149" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA149" s="10" t="n">
         <v>1</v>
@@ -15192,7 +15192,7 @@
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>10</v>
@@ -15262,8 +15262,8 @@
       <c r="Y150" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z150" s="9" t="n">
-        <v>0</v>
+      <c r="Z150" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA150" s="10" t="n">
         <v>1</v>
@@ -15580,7 +15580,7 @@
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F154" s="6" t="n">
         <v>10</v>
@@ -15650,8 +15650,8 @@
       <c r="Y154" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z154" s="9" t="n">
-        <v>0</v>
+      <c r="Z154" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA154" s="10" t="n">
         <v>1</v>
@@ -15774,7 +15774,7 @@
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F156" s="6" t="n">
         <v>10</v>
@@ -15815,7 +15815,7 @@
         </is>
       </c>
       <c r="P156" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q156" s="9" t="n">
         <v>0</v>
@@ -15844,8 +15844,8 @@
       <c r="Y156" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z156" s="9" t="n">
-        <v>0</v>
+      <c r="Z156" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA156" s="10" t="n">
         <v>1</v>
@@ -16065,7 +16065,7 @@
         </is>
       </c>
       <c r="E159" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F159" s="6" t="n">
         <v>10</v>
@@ -16120,8 +16120,8 @@
       <c r="T159" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U159" s="9" t="n">
-        <v>0</v>
+      <c r="U159" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V159" s="9" t="n">
         <v>1</v>
@@ -16259,7 +16259,7 @@
         </is>
       </c>
       <c r="E161" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F161" s="6" t="n">
         <v>10</v>
@@ -16329,8 +16329,8 @@
       <c r="Y161" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z161" s="9" t="n">
-        <v>0</v>
+      <c r="Z161" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA161" s="10" t="n">
         <v>1</v>
@@ -16744,7 +16744,7 @@
         </is>
       </c>
       <c r="E166" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F166" s="6" t="n">
         <v>10</v>
@@ -16814,8 +16814,8 @@
       <c r="Y166" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z166" s="9" t="n">
-        <v>0</v>
+      <c r="Z166" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA166" s="10" t="n">
         <v>1</v>
@@ -16938,7 +16938,7 @@
         </is>
       </c>
       <c r="E168" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F168" s="6" t="n">
         <v>10</v>
@@ -17008,8 +17008,8 @@
       <c r="Y168" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z168" s="9" t="n">
-        <v>0</v>
+      <c r="Z168" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA168" s="10" t="n">
         <v>1</v>
@@ -17132,7 +17132,7 @@
         </is>
       </c>
       <c r="E170" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F170" s="6" t="n">
         <v>10</v>
@@ -17202,8 +17202,8 @@
       <c r="Y170" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z170" s="9" t="n">
-        <v>0</v>
+      <c r="Z170" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA170" s="10" t="n">
         <v>1</v>
@@ -17811,7 +17811,7 @@
         </is>
       </c>
       <c r="E177" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F177" s="6" t="n">
         <v>10</v>
@@ -17881,8 +17881,8 @@
       <c r="Y177" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z177" s="9" t="n">
-        <v>0</v>
+      <c r="Z177" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA177" s="10" t="n">
         <v>1</v>
@@ -18170,7 +18170,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -18203,7 +18203,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -18269,7 +18269,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -18302,7 +18302,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -18335,7 +18335,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -18401,7 +18401,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -18500,7 +18500,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -18533,7 +18533,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -18566,7 +18566,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -18599,7 +18599,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -18632,7 +18632,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -18665,7 +18665,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -18698,7 +18698,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -18731,7 +18731,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -18797,7 +18797,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -18830,7 +18830,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -18863,7 +18863,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -18896,7 +18896,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -18929,7 +18929,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -18962,7 +18962,7 @@
         <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -19028,7 +19028,7 @@
         <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -19094,7 +19094,7 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -19127,7 +19127,7 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -19160,7 +19160,7 @@
         <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -19175,7 +19175,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -19226,7 +19226,7 @@
         <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -19259,7 +19259,7 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -19292,7 +19292,7 @@
         <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -19325,7 +19325,7 @@
         <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -19358,7 +19358,7 @@
         <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -19391,7 +19391,7 @@
         <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -19424,7 +19424,7 @@
         <v>5</v>
       </c>
       <c r="D40" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>

--- a/docs/d/218/inyear.xlsx
+++ b/docs/d/218/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 9 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 9 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 33 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 34 clubs short</t>
         </is>
       </c>
     </row>
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -1141,13 +1141,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="V5" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W5" s="9" t="n">
         <v>0</v>
@@ -1238,13 +1238,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>10</v>
@@ -1335,17 +1335,17 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M7" s="8" t="n">
@@ -1379,8 +1379,8 @@
       <c r="U7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V7" s="9" t="n">
-        <v>0</v>
+      <c r="V7" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W7" s="9" t="n">
         <v>0</v>
@@ -1432,13 +1432,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1529,13 +1529,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -1585,8 +1585,8 @@
       <c r="Y9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z9" s="10" t="n">
-        <v>1</v>
+      <c r="Z9" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA9" s="10" t="n">
         <v>1</v>
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
@@ -1670,8 +1670,8 @@
       <c r="U10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V10" s="9" t="n">
-        <v>0</v>
+      <c r="V10" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W10" s="9" t="n">
         <v>0</v>
@@ -1723,13 +1723,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2111,17 +2111,17 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M15" s="8" t="n">
@@ -2208,13 +2208,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
@@ -2305,17 +2305,17 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M17" s="8" t="n">
@@ -2402,13 +2402,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
@@ -2499,13 +2499,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>0</v>
       </c>
       <c r="V19" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19" s="9" t="n">
         <v>0</v>
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>10</v>
@@ -2596,17 +2596,17 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M20" s="8" t="n">
@@ -2637,8 +2637,8 @@
       <c r="T20" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U20" s="9" t="n">
-        <v>0</v>
+      <c r="U20" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V20" s="9" t="n">
         <v>1</v>
@@ -2693,17 +2693,17 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M21" s="8" t="n">
@@ -2790,13 +2790,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>3</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
@@ -2984,13 +2984,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
@@ -3081,13 +3081,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>0</v>
       </c>
       <c r="V25" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W25" s="9" t="n">
         <v>0</v>
@@ -3178,13 +3178,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -3275,13 +3275,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>0</v>
       </c>
       <c r="V27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W27" s="9" t="n">
         <v>0</v>
@@ -3372,13 +3372,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
@@ -3469,13 +3469,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
@@ -3566,17 +3566,17 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M30" s="8" t="n">
@@ -3649,7 +3649,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3663,13 +3663,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
@@ -3695,8 +3695,8 @@
       <c r="Q31" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R31" s="9" t="n">
-        <v>1</v>
+      <c r="R31" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S31" s="9" t="n">
         <v>1</v>
@@ -3707,8 +3707,8 @@
       <c r="U31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V31" s="9" t="n">
-        <v>2</v>
+      <c r="V31" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>0</v>
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32" s="6" t="n">
         <v>10</v>
@@ -3760,13 +3760,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
@@ -3804,11 +3804,11 @@
       <c r="U32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V32" s="9" t="n">
-        <v>3</v>
+      <c r="V32" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W32" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X32" s="10" t="n">
         <v>7</v>
@@ -3857,17 +3857,17 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L33" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M33" s="8" t="n">
@@ -3954,13 +3954,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
@@ -4148,13 +4148,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
@@ -4245,13 +4245,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>0</v>
       </c>
       <c r="V37" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W37" s="9" t="n">
         <v>0</v>
@@ -4342,17 +4342,17 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L38" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L38" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M38" s="8" t="n">
@@ -4369,7 +4369,7 @@
         </is>
       </c>
       <c r="P38" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q38" s="9" t="n">
         <v>0</v>
@@ -4439,13 +4439,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
@@ -4536,13 +4536,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>41</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>2</v>
+        <v>-14</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>0</v>
       </c>
       <c r="V41" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W41" s="9" t="n">
         <v>0</v>
@@ -4730,13 +4730,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
@@ -4924,17 +4924,17 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L44" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L44" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M44" s="8" t="n">
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5118,17 +5118,17 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L46" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L46" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M46" s="8" t="n">
@@ -5165,8 +5165,8 @@
       <c r="V46" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W46" s="9" t="n">
-        <v>1</v>
+      <c r="W46" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X46" s="9" t="n">
         <v>1</v>
@@ -5215,13 +5215,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>10</v>
@@ -5312,13 +5312,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>41</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>3</v>
+        <v>-6</v>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
@@ -5356,8 +5356,8 @@
       <c r="U48" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="V48" s="9" t="n">
-        <v>3</v>
+      <c r="V48" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W48" s="9" t="n">
         <v>0</v>
@@ -5409,17 +5409,17 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L49" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M49" s="8" t="n">
@@ -5506,17 +5506,17 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L50" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L50" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M50" s="8" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
@@ -5797,13 +5797,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>0</v>
       </c>
       <c r="V53" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W53" s="9" t="n">
         <v>0</v>
@@ -5894,17 +5894,17 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L54" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-15</v>
+      </c>
+      <c r="L54" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M54" s="8" t="n">
@@ -5977,7 +5977,7 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>10</v>
@@ -5991,17 +5991,17 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>12</v>
+      </c>
+      <c r="L55" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M55" s="8" t="n">
@@ -6035,11 +6035,11 @@
       <c r="U55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V55" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W55" s="9" t="n">
-        <v>0</v>
+      <c r="V55" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W55" s="10" t="n">
+        <v>11</v>
       </c>
       <c r="X55" s="9" t="n">
         <v>3</v>
@@ -6282,13 +6282,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
@@ -6476,13 +6476,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
@@ -6573,13 +6573,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -6670,13 +6670,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -6864,17 +6864,17 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L64" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L64" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M64" s="8" t="n">
@@ -6961,13 +6961,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
@@ -7058,17 +7058,17 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L66" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M66" s="8" t="n">
@@ -7103,7 +7103,7 @@
         <v>0</v>
       </c>
       <c r="V66" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W66" s="9" t="n">
         <v>0</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
@@ -7252,17 +7252,17 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L68" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L68" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M68" s="8" t="n">
@@ -7349,13 +7349,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         <v>0</v>
       </c>
       <c r="V69" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W69" s="9" t="n">
         <v>0</v>
@@ -7446,13 +7446,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -7543,13 +7543,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
@@ -7640,13 +7640,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -7737,13 +7737,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
@@ -7834,17 +7834,17 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L74" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M74" s="8" t="n">
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
@@ -8028,13 +8028,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>0</v>
       </c>
       <c r="V76" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W76" s="9" t="n">
         <v>0</v>
@@ -8125,13 +8125,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>0</v>
       </c>
       <c r="V77" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W77" s="9" t="n">
         <v>0</v>
@@ -8222,13 +8222,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8319,13 +8319,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
@@ -8416,13 +8416,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>0</v>
       </c>
       <c r="V80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W80" s="9" t="n">
         <v>0</v>
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
@@ -8610,17 +8610,17 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L82" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L82" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M82" s="8" t="n">
@@ -8655,7 +8655,7 @@
         <v>0</v>
       </c>
       <c r="V82" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W82" s="9" t="n">
         <v>0</v>
@@ -8707,13 +8707,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>0</v>
       </c>
       <c r="V83" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W83" s="9" t="n">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
@@ -8901,13 +8901,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
@@ -8998,13 +8998,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L86" s="7" t="inlineStr">
         <is>
@@ -9095,13 +9095,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
@@ -9192,13 +9192,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         <v>0</v>
       </c>
       <c r="V88" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W88" s="9" t="n">
         <v>0</v>
@@ -9289,17 +9289,17 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L89" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L89" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M89" s="8" t="n">
@@ -9334,7 +9334,7 @@
         <v>0</v>
       </c>
       <c r="V89" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W89" s="9" t="n">
         <v>0</v>
@@ -9483,13 +9483,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
@@ -9580,13 +9580,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
@@ -9677,13 +9677,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
@@ -9774,13 +9774,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -9871,13 +9871,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>4</v>
       </c>
       <c r="W95" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X95" s="10" t="n">
         <v>7</v>
@@ -9968,13 +9968,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         <v>0</v>
       </c>
       <c r="V96" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W96" s="9" t="n">
         <v>0</v>
@@ -10065,17 +10065,17 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L97" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L97" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M97" s="8" t="n">
@@ -10162,13 +10162,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
@@ -10259,13 +10259,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
@@ -10356,13 +10356,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -10453,13 +10453,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>0</v>
       </c>
       <c r="V101" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W101" s="9" t="n">
         <v>0</v>
@@ -10536,7 +10536,7 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -10550,13 +10550,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
@@ -10588,8 +10588,8 @@
       <c r="S102" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T102" s="9" t="n">
-        <v>0</v>
+      <c r="T102" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U102" s="9" t="n">
         <v>0</v>
@@ -10744,17 +10744,17 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L104" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M104" s="8" t="n">
@@ -10789,7 +10789,7 @@
         <v>1</v>
       </c>
       <c r="V104" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W104" s="9" t="n">
         <v>0</v>
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -10938,13 +10938,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
@@ -10973,8 +10973,8 @@
       <c r="R106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S106" s="9" t="n">
-        <v>1</v>
+      <c r="S106" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T106" s="9" t="n">
         <v>0</v>
@@ -11035,13 +11035,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
@@ -11132,17 +11132,17 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L108" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L108" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M108" s="8" t="n">
@@ -11229,17 +11229,17 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L109" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L109" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M109" s="8" t="n">
@@ -11326,17 +11326,17 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L110" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L110" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M110" s="8" t="n">
@@ -11371,7 +11371,7 @@
         <v>0</v>
       </c>
       <c r="V110" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W110" s="9" t="n">
         <v>0</v>
@@ -11423,13 +11423,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
@@ -11520,13 +11520,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L112" s="7" t="inlineStr">
         <is>
@@ -11617,17 +11617,17 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L113" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L113" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M113" s="8" t="n">
@@ -11644,7 +11644,7 @@
         </is>
       </c>
       <c r="P113" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q113" s="9" t="n">
         <v>0</v>
@@ -11714,13 +11714,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -11811,13 +11811,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
@@ -11838,7 +11838,7 @@
         </is>
       </c>
       <c r="P115" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q115" s="9" t="n">
         <v>0</v>
@@ -11908,13 +11908,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>0</v>
       </c>
       <c r="V116" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W116" s="9" t="n">
         <v>0</v>
@@ -12005,13 +12005,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>0</v>
       </c>
       <c r="V117" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W117" s="9" t="n">
         <v>0</v>
@@ -12102,13 +12102,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L118" s="7" t="inlineStr">
         <is>
@@ -12199,13 +12199,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
@@ -12296,13 +12296,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
@@ -12393,13 +12393,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
@@ -12490,13 +12490,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
         <v>0</v>
       </c>
       <c r="V122" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W122" s="9" t="n">
         <v>0</v>
@@ -12587,17 +12587,17 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L123" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L123" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M123" s="8" t="n">
@@ -12632,7 +12632,7 @@
         <v>0</v>
       </c>
       <c r="V123" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W123" s="9" t="n">
         <v>0</v>
@@ -12684,13 +12684,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -12781,13 +12781,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="L125" s="4" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>4</v>
       </c>
       <c r="W125" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X125" s="10" t="n">
         <v>5</v>
@@ -12864,7 +12864,7 @@
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -12878,13 +12878,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>3</v>
+        <v>-8</v>
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
@@ -12922,8 +12922,8 @@
       <c r="U126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V126" s="9" t="n">
-        <v>3</v>
+      <c r="V126" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W126" s="9" t="n">
         <v>0</v>
@@ -12975,13 +12975,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="L127" s="4" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
         </is>
       </c>
       <c r="P127" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q127" s="9" t="n">
         <v>0</v>
@@ -13072,13 +13072,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
@@ -13169,13 +13169,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L129" s="7" t="inlineStr">
         <is>
@@ -13266,13 +13266,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L130" s="7" t="inlineStr">
         <is>
@@ -13363,13 +13363,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
@@ -13460,13 +13460,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
@@ -13557,13 +13557,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>3</v>
+        <v>-6</v>
       </c>
       <c r="L133" s="4" t="inlineStr">
         <is>
@@ -13751,17 +13751,17 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L135" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L135" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M135" s="8" t="n">
@@ -13796,7 +13796,7 @@
         <v>0</v>
       </c>
       <c r="V135" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W135" s="9" t="n">
         <v>0</v>
@@ -13834,7 +13834,7 @@
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -13848,13 +13848,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>7</v>
+        <v>-5</v>
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
@@ -13895,8 +13895,8 @@
       <c r="V136" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W136" s="9" t="n">
-        <v>3</v>
+      <c r="W136" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X136" s="10" t="n">
         <v>7</v>
@@ -13931,7 +13931,7 @@
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>10</v>
@@ -13989,11 +13989,11 @@
       <c r="U137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V137" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W137" s="9" t="n">
-        <v>0</v>
+      <c r="V137" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W137" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X137" s="10" t="n">
         <v>7</v>
@@ -14042,13 +14042,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>1</v>
+        <v>-9</v>
       </c>
       <c r="L138" s="7" t="inlineStr">
         <is>
@@ -14139,17 +14139,17 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L139" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L139" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M139" s="8" t="n">
@@ -14166,7 +14166,7 @@
         </is>
       </c>
       <c r="P139" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q139" s="9" t="n">
         <v>0</v>
@@ -14222,7 +14222,7 @@
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F140" s="6" t="n">
         <v>10</v>
@@ -14236,13 +14236,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
@@ -14280,11 +14280,11 @@
       <c r="U140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V140" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W140" s="9" t="n">
-        <v>0</v>
+      <c r="V140" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W140" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X140" s="9" t="n">
         <v>3</v>
@@ -14333,13 +14333,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L141" s="4" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F142" s="6" t="n">
         <v>10</v>
@@ -14430,13 +14430,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
@@ -14477,8 +14477,8 @@
       <c r="V142" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W142" s="9" t="n">
-        <v>1</v>
+      <c r="W142" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X142" s="10" t="n">
         <v>7</v>
@@ -14527,13 +14527,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
@@ -14624,17 +14624,17 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L144" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L144" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M144" s="8" t="n">
@@ -14721,17 +14721,17 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L145" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L145" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M145" s="8" t="n">
@@ -14748,7 +14748,7 @@
         </is>
       </c>
       <c r="P145" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q145" s="9" t="n">
         <v>0</v>
@@ -14766,7 +14766,7 @@
         <v>0</v>
       </c>
       <c r="V145" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W145" s="9" t="n">
         <v>0</v>
@@ -14818,13 +14818,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L146" s="7" t="inlineStr">
         <is>
@@ -14915,13 +14915,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L147" s="7" t="inlineStr">
         <is>
@@ -15012,17 +15012,17 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L148" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-15</v>
+      </c>
+      <c r="L148" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M148" s="8" t="n">
@@ -15109,13 +15109,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="L149" s="7" t="inlineStr">
         <is>
@@ -15154,7 +15154,7 @@
         <v>0</v>
       </c>
       <c r="V149" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W149" s="9" t="n">
         <v>0</v>
@@ -15206,13 +15206,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L150" s="7" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         <v>0</v>
       </c>
       <c r="V150" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W150" s="9" t="n">
         <v>0</v>
@@ -15303,13 +15303,13 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L151" s="7" t="inlineStr">
         <is>
@@ -15400,13 +15400,13 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L152" s="4" t="inlineStr">
         <is>
@@ -15448,7 +15448,7 @@
         <v>4</v>
       </c>
       <c r="W152" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X152" s="10" t="n">
         <v>7</v>
@@ -15497,13 +15497,13 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L153" s="7" t="inlineStr">
         <is>
@@ -15594,13 +15594,13 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L154" s="7" t="inlineStr">
         <is>
@@ -15691,13 +15691,13 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L155" s="7" t="inlineStr">
         <is>
@@ -15788,13 +15788,13 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L156" s="7" t="inlineStr">
         <is>
@@ -15885,13 +15885,13 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L157" s="7" t="inlineStr">
         <is>
@@ -15982,13 +15982,13 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="J158" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>4</v>
+        <v>-8</v>
       </c>
       <c r="L158" s="4" t="inlineStr">
         <is>
@@ -16079,17 +16079,17 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J159" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L159" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L159" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M159" s="8" t="n">
@@ -16273,13 +16273,13 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L161" s="7" t="inlineStr">
         <is>
@@ -16318,7 +16318,7 @@
         <v>0</v>
       </c>
       <c r="V161" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W161" s="9" t="n">
         <v>0</v>
@@ -16467,13 +16467,13 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="J163" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="L163" s="4" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         </is>
       </c>
       <c r="P163" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q163" s="10" t="n">
         <v>2</v>
@@ -16503,7 +16503,7 @@
         <v>0</v>
       </c>
       <c r="S163" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T163" s="9" t="n">
         <v>0</v>
@@ -16512,7 +16512,7 @@
         <v>0</v>
       </c>
       <c r="V163" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W163" s="9" t="n">
         <v>0</v>
@@ -16564,13 +16564,13 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J164" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L164" s="7" t="inlineStr">
         <is>
@@ -16661,13 +16661,13 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J165" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K165" s="4" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="L165" s="7" t="inlineStr">
         <is>
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J166" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K166" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L166" s="7" t="inlineStr">
         <is>
@@ -16803,7 +16803,7 @@
         <v>0</v>
       </c>
       <c r="V166" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W166" s="9" t="n">
         <v>0</v>
@@ -16855,13 +16855,13 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J167" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L167" s="7" t="inlineStr">
         <is>
@@ -16952,13 +16952,13 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J168" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L168" s="7" t="inlineStr">
         <is>
@@ -17049,13 +17049,13 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="J169" s="4" t="n">
         <v>41</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L169" s="4" t="inlineStr">
         <is>
@@ -17146,13 +17146,13 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J170" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L170" s="7" t="inlineStr">
         <is>
@@ -17243,13 +17243,13 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J171" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L171" s="7" t="inlineStr">
         <is>
@@ -17340,13 +17340,13 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J172" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K172" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L172" s="7" t="inlineStr">
         <is>
@@ -17437,13 +17437,13 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J173" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K173" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L173" s="7" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>0</v>
       </c>
       <c r="V173" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W173" s="9" t="n">
         <v>0</v>
@@ -17534,13 +17534,13 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J174" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K174" s="4" t="n">
-        <v>-8</v>
+        <v>-14</v>
       </c>
       <c r="L174" s="7" t="inlineStr">
         <is>
@@ -17631,17 +17631,17 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J175" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K175" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L175" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L175" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M175" s="8" t="n">
@@ -17728,13 +17728,13 @@
         </is>
       </c>
       <c r="I176" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J176" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K176" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L176" s="7" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>0</v>
       </c>
       <c r="V176" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W176" s="9" t="n">
         <v>0</v>
@@ -17825,13 +17825,13 @@
         </is>
       </c>
       <c r="I177" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J177" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K177" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L177" s="7" t="inlineStr">
         <is>
@@ -17870,7 +17870,7 @@
         <v>0</v>
       </c>
       <c r="V177" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W177" s="9" t="n">
         <v>0</v>
@@ -17922,13 +17922,13 @@
         </is>
       </c>
       <c r="I178" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J178" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K178" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L178" s="7" t="inlineStr">
         <is>
@@ -17967,7 +17967,7 @@
         <v>0</v>
       </c>
       <c r="V178" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W178" s="9" t="n">
         <v>0</v>
@@ -18019,17 +18019,17 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J179" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K179" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L179" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L179" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M179" s="8" t="n">
@@ -18218,7 +18218,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -18236,7 +18236,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -18284,7 +18284,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -18302,7 +18302,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -18317,7 +18317,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -18368,13 +18368,13 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -18383,7 +18383,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -18401,7 +18401,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -18416,7 +18416,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -18449,7 +18449,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -18482,7 +18482,7 @@
         <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -18500,7 +18500,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -18515,7 +18515,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -18548,7 +18548,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -18566,7 +18566,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -18581,7 +18581,7 @@
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -18614,7 +18614,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -18680,7 +18680,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -18746,7 +18746,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -18812,7 +18812,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -18845,7 +18845,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -18896,7 +18896,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -18911,7 +18911,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -18944,7 +18944,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -18977,7 +18977,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -19043,7 +19043,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -19061,7 +19061,7 @@
         <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -19127,13 +19127,13 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -19142,7 +19142,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -19160,7 +19160,7 @@
         <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -19175,7 +19175,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -19208,7 +19208,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -19241,7 +19241,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -19307,7 +19307,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -19439,7 +19439,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/218/inyear.xlsx
+++ b/docs/d/218/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/218/inyear.xlsx
+++ b/docs/d/218/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/218/inyear.xlsx
+++ b/docs/d/218/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/218/inyear.xlsx
+++ b/docs/d/218/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/218/inyear.xlsx
+++ b/docs/d/218/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 9 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 9 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 34 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 34 clubs short</t>
         </is>
       </c>
     </row>
@@ -1529,13 +1529,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>0</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>0</v>
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>0</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12" s="9" t="n">
         <v>0</v>
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2343,8 +2343,8 @@
       <c r="S17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T17" s="9" t="n">
-        <v>0</v>
+      <c r="T17" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U17" s="9" t="n">
         <v>0</v>
@@ -2499,13 +2499,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>0</v>
       </c>
       <c r="V19" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W19" s="9" t="n">
         <v>0</v>
@@ -2693,13 +2693,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="V21" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W21" s="9" t="n">
         <v>0</v>
@@ -3178,13 +3178,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>0</v>
       </c>
       <c r="V26" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W26" s="9" t="n">
         <v>0</v>
@@ -3760,13 +3760,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
@@ -4342,13 +4342,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>41</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -4730,13 +4730,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
@@ -4924,13 +4924,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>-13</v>
+        <v>-11</v>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
@@ -5118,13 +5118,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>4</v>
       </c>
       <c r="W46" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X46" s="9" t="n">
         <v>1</v>
@@ -5354,7 +5354,7 @@
         <v>1</v>
       </c>
       <c r="U48" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V48" s="10" t="n">
         <v>4</v>
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6517,8 +6517,8 @@
       <c r="T60" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U60" s="9" t="n">
-        <v>0</v>
+      <c r="U60" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V60" s="9" t="n">
         <v>0</v>
@@ -6603,7 +6603,7 @@
         <v>1</v>
       </c>
       <c r="Q61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R61" s="9" t="n">
         <v>0</v>
@@ -6670,13 +6670,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>0</v>
       </c>
       <c r="Q64" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R64" s="9" t="n">
         <v>0</v>
@@ -7058,13 +7058,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
@@ -7252,17 +7252,17 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>-12</v>
-      </c>
-      <c r="L68" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-8</v>
+      </c>
+      <c r="L68" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M68" s="8" t="n">
@@ -7288,7 +7288,7 @@
         <v>0</v>
       </c>
       <c r="S68" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T68" s="9" t="n">
         <v>0</v>
@@ -7543,13 +7543,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
@@ -7640,13 +7640,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8163,8 +8163,8 @@
       <c r="S77" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T77" s="9" t="n">
-        <v>0</v>
+      <c r="T77" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U77" s="9" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -8645,8 +8645,8 @@
       <c r="R82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S82" s="9" t="n">
-        <v>1</v>
+      <c r="S82" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T82" s="10" t="n">
         <v>1</v>
@@ -8984,7 +8984,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -8998,13 +8998,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="7" t="inlineStr">
         <is>
@@ -9042,8 +9042,8 @@
       <c r="U86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V86" s="9" t="n">
-        <v>3</v>
+      <c r="V86" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W86" s="9" t="n">
         <v>0</v>
@@ -9192,13 +9192,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
@@ -9677,13 +9677,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
@@ -9722,7 +9722,7 @@
         <v>0</v>
       </c>
       <c r="V93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W93" s="9" t="n">
         <v>0</v>
@@ -9898,7 +9898,7 @@
         </is>
       </c>
       <c r="P95" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q95" s="9" t="n">
         <v>1</v>
@@ -9968,13 +9968,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10065,13 +10065,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
@@ -10356,13 +10356,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -10579,8 +10579,8 @@
       <c r="P102" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q102" s="9" t="n">
-        <v>1</v>
+      <c r="Q102" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R102" s="9" t="n">
         <v>0</v>
@@ -10591,8 +10591,8 @@
       <c r="T102" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U102" s="9" t="n">
-        <v>0</v>
+      <c r="U102" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V102" s="10" t="n">
         <v>4</v>
@@ -10774,13 +10774,13 @@
         <v>1</v>
       </c>
       <c r="Q104" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R104" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S104" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T104" s="10" t="n">
         <v>1</v>
@@ -11021,7 +11021,7 @@
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>10</v>
@@ -11073,8 +11073,8 @@
       <c r="S107" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T107" s="9" t="n">
-        <v>0</v>
+      <c r="T107" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U107" s="9" t="n">
         <v>0</v>
@@ -11132,13 +11132,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         </is>
       </c>
       <c r="P117" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q117" s="9" t="n">
         <v>0</v>
@@ -12684,13 +12684,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
         </is>
       </c>
       <c r="P124" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q124" s="9" t="n">
         <v>0</v>
@@ -12878,13 +12878,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
@@ -14721,17 +14721,17 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L145" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L145" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M145" s="8" t="n">
@@ -15427,7 +15427,7 @@
         </is>
       </c>
       <c r="P152" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q152" s="9" t="n">
         <v>0</v>
@@ -16273,13 +16273,13 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L161" s="7" t="inlineStr">
         <is>
@@ -16467,13 +16467,13 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J163" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L163" s="4" t="inlineStr">
         <is>
@@ -16564,13 +16564,13 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J164" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="L164" s="7" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>0</v>
       </c>
       <c r="Q164" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R164" s="9" t="n">
         <v>0</v>
@@ -16609,7 +16609,7 @@
         <v>0</v>
       </c>
       <c r="V164" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W164" s="9" t="n">
         <v>0</v>
@@ -17079,7 +17079,7 @@
         <v>1</v>
       </c>
       <c r="Q169" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R169" s="9" t="n">
         <v>0</v>
@@ -17340,13 +17340,13 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J172" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K172" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L172" s="7" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>0</v>
       </c>
       <c r="V172" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W172" s="9" t="n">
         <v>0</v>
@@ -17534,13 +17534,13 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J174" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K174" s="4" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="L174" s="7" t="inlineStr">
         <is>
@@ -17631,13 +17631,13 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J175" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K175" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L175" s="7" t="inlineStr">
         <is>
@@ -17825,13 +17825,13 @@
         </is>
       </c>
       <c r="I177" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J177" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K177" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L177" s="7" t="inlineStr">
         <is>
@@ -18019,13 +18019,13 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J179" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K179" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L179" s="7" t="inlineStr">
         <is>
@@ -18269,7 +18269,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -18599,7 +18599,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -18647,7 +18647,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -18698,7 +18698,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -18731,7 +18731,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -18764,7 +18764,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -18896,13 +18896,13 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -18929,7 +18929,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -19208,7 +19208,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
